--- a/01_INPUTS/objetivo 11T.xlsx
+++ b/01_INPUTS/objetivo 11T.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E45725C-8FB5-495A-AC08-EEB2EF95F341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937C5C1D-A6CC-4168-BB91-9599E2F0BF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2756557E-6E43-4FBF-8971-227ACF024C24}"/>
   </bookViews>
@@ -447,7 +447,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>639</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -455,7 +455,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>137</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -463,7 +463,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>384</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -471,7 +471,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>440</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -487,7 +487,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>467</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
@@ -495,7 +495,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1">
-        <v>317</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -503,7 +503,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1">
-        <v>396</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
@@ -511,7 +511,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>190</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -519,7 +519,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
-        <v>400</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="1">
-        <v>122</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/01_INPUTS/objetivo 11T.xlsx
+++ b/01_INPUTS/objetivo 11T.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937C5C1D-A6CC-4168-BB91-9599E2F0BF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0AAC34-9103-40AD-8CF0-10626A65D7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2756557E-6E43-4FBF-8971-227ACF024C24}"/>
   </bookViews>
@@ -447,7 +447,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>318</v>
+        <v>636</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
@@ -455,7 +455,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>106</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
@@ -463,7 +463,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>189</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -471,7 +471,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>216</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
@@ -479,7 +479,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1">
-        <v>46</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
@@ -487,7 +487,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>254</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
@@ -495,7 +495,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1">
-        <v>193</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
@@ -503,7 +503,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1">
-        <v>199</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
@@ -511,7 +511,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>95</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
@@ -519,7 +519,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1">
-        <v>196</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="1">
-        <v>52</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/01_INPUTS/objetivo 11T.xlsx
+++ b/01_INPUTS/objetivo 11T.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0AAC34-9103-40AD-8CF0-10626A65D7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9C5265-1953-41BF-B78F-F13A9D24ED49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2756557E-6E43-4FBF-8971-227ACF024C24}"/>
   </bookViews>
@@ -36,43 +36,43 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>Alma Mora</t>
-  </si>
-  <si>
     <t>Trapiche Reserva</t>
   </si>
   <si>
-    <t>Finca las moras</t>
-  </si>
-  <si>
-    <t>Alaris</t>
-  </si>
-  <si>
-    <t>Don David</t>
-  </si>
-  <si>
-    <t>Dada</t>
-  </si>
-  <si>
-    <t>Simrnoff Flavors</t>
-  </si>
-  <si>
-    <t>Los Arboles</t>
-  </si>
-  <si>
-    <t>Antares</t>
-  </si>
-  <si>
-    <t>Smirnoff ice</t>
-  </si>
-  <si>
-    <t>Gordons flavours</t>
-  </si>
-  <si>
     <t>Linea comercial</t>
   </si>
   <si>
     <t>Objetivo</t>
+  </si>
+  <si>
+    <t>ALARIS</t>
+  </si>
+  <si>
+    <t>ALMA MORA</t>
+  </si>
+  <si>
+    <t>ANTARES</t>
+  </si>
+  <si>
+    <t>DADA</t>
+  </si>
+  <si>
+    <t>DON DAVID</t>
+  </si>
+  <si>
+    <t>FINCA LAS MORAS</t>
+  </si>
+  <si>
+    <t>GORDONS FLAVOURS</t>
+  </si>
+  <si>
+    <t>LOS ARBOLES</t>
+  </si>
+  <si>
+    <t>SMIRNOFF FLAVORS</t>
+  </si>
+  <si>
+    <t>SMIRNOFF ICE</t>
   </si>
 </sst>
 </file>
@@ -88,15 +88,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,14 +110,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,98 +476,98 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1">
-        <v>636</v>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>212</v>
+        <v>4</v>
+      </c>
+      <c r="C4" s="4">
+        <v>909</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>378</v>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>433</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>728</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>92</v>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3">
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>509</v>
+        <v>8</v>
+      </c>
+      <c r="C8" s="4">
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1">
-        <v>387</v>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3">
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
-        <v>399</v>
+        <v>10</v>
+      </c>
+      <c r="C10" s="4">
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1">
-        <v>191</v>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3">
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="1">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1">
-        <v>104</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="4">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
